--- a/Data/Skill.xlsx
+++ b/Data/Skill.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28129"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GoldenMansion\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CB0AC4E-9094-49F9-8B96-ED53BF5E59A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D350F324-114D-4938-95E4-C879561F6317}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="223" uniqueCount="111">
   <si>
     <t>ID</t>
   </si>
@@ -74,341 +74,351 @@
     <t>外向</t>
   </si>
   <si>
+    <t>细心</t>
+  </si>
+  <si>
+    <t>抽象</t>
+  </si>
+  <si>
+    <t>感性</t>
+  </si>
+  <si>
+    <t>每有房客被卖出时，有概率离开</t>
+  </si>
+  <si>
+    <t>理性</t>
+  </si>
+  <si>
+    <t>无法被消除</t>
+  </si>
+  <si>
+    <t>循规蹈矩</t>
+  </si>
+  <si>
+    <t>每回合结束后，租金+1</t>
+  </si>
+  <si>
+    <t>随性</t>
+  </si>
+  <si>
+    <t>INTJ</t>
+  </si>
+  <si>
+    <t>每有一个房客被卖出后，所有租客房租+1</t>
+  </si>
+  <si>
+    <t>INTP</t>
+  </si>
+  <si>
+    <t>ENTJ</t>
+  </si>
+  <si>
+    <t>ENTP</t>
+  </si>
+  <si>
+    <t>INFJ</t>
+  </si>
+  <si>
+    <t>每回合结束后，所有租客房租+1</t>
+  </si>
+  <si>
+    <t>INFP</t>
+  </si>
+  <si>
+    <t>持续生效：买入租客的价格降低50%</t>
+  </si>
+  <si>
+    <t>ENFJ</t>
+  </si>
+  <si>
+    <t>ENFP</t>
+  </si>
+  <si>
+    <t>交租时，每有一个外向型，房租+1</t>
+  </si>
+  <si>
+    <t>ISTJ</t>
+  </si>
+  <si>
+    <t>交租后，每有5元余额，额外获得1元</t>
+  </si>
+  <si>
+    <t>ISFJ</t>
+  </si>
+  <si>
+    <t>ESTJ</t>
+  </si>
+  <si>
+    <t>ESFJ</t>
+  </si>
+  <si>
+    <t>持续生效：使所有实习生房租+1</t>
+  </si>
+  <si>
+    <t>ISTP</t>
+  </si>
+  <si>
+    <t>ISFP</t>
+  </si>
+  <si>
+    <t>持续生效：交租时，空房间也可提供+5租金</t>
+  </si>
+  <si>
+    <t>ESTP</t>
+  </si>
+  <si>
+    <t>ESFP</t>
+  </si>
+  <si>
+    <t>学生党</t>
+  </si>
+  <si>
+    <t>金融</t>
+  </si>
+  <si>
+    <t>游戏</t>
+  </si>
+  <si>
+    <t>自由职业</t>
+  </si>
+  <si>
+    <t>教育哥</t>
+  </si>
+  <si>
+    <t>电商哥</t>
+  </si>
+  <si>
+    <t>体育哥</t>
+  </si>
+  <si>
+    <t>房地产</t>
+  </si>
+  <si>
+    <t>艺术哥</t>
+  </si>
+  <si>
+    <t>餐饮哥</t>
+  </si>
+  <si>
+    <t>媒体哥</t>
+  </si>
+  <si>
+    <t>旅游哥</t>
+  </si>
+  <si>
+    <t>珠宝哥</t>
+  </si>
+  <si>
+    <t>医疗哥</t>
+  </si>
+  <si>
+    <t>无业</t>
+  </si>
+  <si>
+    <t>#&lt;------</t>
+  </si>
+  <si>
+    <t>入住后，消除自身周围的人</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>int[]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>条件数值</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>效果数值</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>conditionValue</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>effectValue</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-1000,1000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1,2,3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1000,1500,2000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>500</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>5,10,15</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1,0,-1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10,15,20</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2,3,4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>若没有邻居，租金随机增加1~10</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>若有X个邻居，则租金翻倍（X每天随机）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>获得邻居最高的房租</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>每天，生成一个任意职业的实习生</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>若没有邻居，则生成8个随机租客，然后离开</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>持续生效：交租前，周围每有一个空房间，租金+10</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>若基础租金比所有邻居都高，则让邻居租金等于他的租金</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>若所有邻居都是ESFP，这局游戏胜利</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>使其邻居的售价永久+1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>移除房租比他低的邻居</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>结算</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>震动</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>商店</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>不需要</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>增加一次重掷机会</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>被卖出时，自身价格翻倍</t>
-  </si>
-  <si>
-    <t>细心</t>
-  </si>
-  <si>
-    <t>抽象</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>交租时，50%的概率忘记交租，50%的概率上交双倍房租</t>
-  </si>
-  <si>
-    <t>感性</t>
-  </si>
-  <si>
-    <t>每有房客被卖出时，有概率离开</t>
-  </si>
-  <si>
-    <t>理性</t>
-  </si>
-  <si>
-    <t>无法被消除</t>
-  </si>
-  <si>
-    <t>循规蹈矩</t>
-  </si>
-  <si>
-    <t>每回合结束后，租金+1</t>
-  </si>
-  <si>
-    <t>随性</t>
-  </si>
-  <si>
-    <t>INTJ</t>
-  </si>
-  <si>
-    <t>每有一个房客被卖出后，所有租客房租+1</t>
-  </si>
-  <si>
-    <t>INTP</t>
-  </si>
-  <si>
-    <t>ENTJ</t>
-  </si>
-  <si>
-    <t>ENTP</t>
-  </si>
-  <si>
-    <t>INFJ</t>
-  </si>
-  <si>
-    <t>每回合结束后，所有租客房租+1</t>
-  </si>
-  <si>
-    <t>INFP</t>
-  </si>
-  <si>
-    <t>持续生效：买入租客的价格降低50%</t>
-  </si>
-  <si>
-    <t>ENFJ</t>
-  </si>
-  <si>
-    <t>ENFP</t>
-  </si>
-  <si>
-    <t>交租时，每有一个外向型，房租+1</t>
-  </si>
-  <si>
-    <t>ISTJ</t>
-  </si>
-  <si>
-    <t>交租后，每有5元余额，额外获得1元</t>
-  </si>
-  <si>
-    <t>ISFJ</t>
-  </si>
-  <si>
-    <t>ESTJ</t>
-  </si>
-  <si>
-    <t>ESFJ</t>
-  </si>
-  <si>
-    <t>持续生效：使所有实习生房租+1</t>
-  </si>
-  <si>
-    <t>ISTP</t>
-  </si>
-  <si>
-    <t>ISFP</t>
-  </si>
-  <si>
-    <t>持续生效：交租时，空房间也可提供+5租金</t>
-  </si>
-  <si>
-    <t>ESTP</t>
-  </si>
-  <si>
-    <t>ESFP</t>
-  </si>
-  <si>
-    <t>学生党</t>
-  </si>
-  <si>
-    <t>持续生效：该系列每有1名租客，他们提供额外租金+1</t>
-  </si>
-  <si>
-    <t>金融</t>
-  </si>
-  <si>
-    <t>持续生效：每有一张被出售的，使该系列租金+1</t>
-  </si>
-  <si>
-    <t>游戏</t>
-  </si>
-  <si>
-    <t>自由职业</t>
-  </si>
-  <si>
-    <t>交租时，没有入住的租客可提供+1租金</t>
-  </si>
-  <si>
-    <t>教育哥</t>
-  </si>
-  <si>
-    <t>持续生效：房租+0，售价+1</t>
-  </si>
-  <si>
-    <t>电商哥</t>
-  </si>
-  <si>
-    <t>持续生效：每次买入租客使其房租+1，每次卖出使其房租-1</t>
-  </si>
-  <si>
-    <t>体育哥</t>
-  </si>
-  <si>
-    <t>交租时：若该系列人数比其他系列人数多，每多1个租金+10</t>
-  </si>
-  <si>
-    <t>房地产</t>
-  </si>
-  <si>
-    <t>艺术哥</t>
-  </si>
-  <si>
-    <t>入住后，每有一名房客被消除，该系列房租+1</t>
-  </si>
-  <si>
-    <t>餐饮哥</t>
-  </si>
-  <si>
-    <t>媒体哥</t>
-  </si>
-  <si>
-    <t>获得后触发：3天内无法买卖租客，然后全体房租提升等同于记者的房租</t>
-  </si>
-  <si>
-    <t>旅游哥</t>
-  </si>
-  <si>
-    <t>交租后：每5次交租使其租金*2</t>
-  </si>
-  <si>
-    <t>珠宝哥</t>
-  </si>
-  <si>
-    <t>医疗哥</t>
-  </si>
-  <si>
-    <t>入住后，若有租客天数超过10天，每一天使该系列租金+2</t>
-  </si>
-  <si>
-    <t>无业</t>
-  </si>
-  <si>
-    <t>交租后：每回合预算-1，无法被出售</t>
-  </si>
-  <si>
-    <t>#&lt;------</t>
-  </si>
-  <si>
-    <t>入住后，消除自身周围的人</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>交租时，所有其他租客租金-1，每有一个租客受影响，该系列房租+1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>int[]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>条件数值</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>效果数值</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>conditionValue</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>effectValue</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>-1000,1000</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1,2,3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1000,1500,2000</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>500</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>5,10,15</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1,0,-1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10,15,20</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2,3,4</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>-1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>增加一次重掷机会</t>
-  </si>
-  <si>
-    <t>若没有邻居，租金随机增加1~10</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>若有X个邻居，则租金翻倍（X每天随机）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>获得邻居最高的房租</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>每天，生成一个任意职业的实习生</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>若没有邻居，则生成8个随机租客，然后离开</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>持续生效：交租前，周围每有一个空房间，租金+10</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>若基础租金比所有邻居都高，则让邻居租金等于他的租金</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>若所有邻居都是ESFP，这局游戏胜利</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>交租时若有3个其他系列人数超过2，租金*2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>每次完成交租，使所有非餐饮住客房租+1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>不提供房租，被消除时，获得所有邻居的售价返还</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>使其邻居的售价永久+1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>移除房租比他低的邻居</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>结算</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>震动</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>商店</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>不需要</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>当学生党人数达到2/3/4时,每名学生党提供额外租金1/2/3.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>当金融哥人数达到2/3/4时,每个被出售的房客,使金融哥租金提升1/2/3.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>当游戏哥人数达到2/3/4时,交租时若有3个其他职业的人数超过3,游戏哥租金提升2/3/4倍</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>当自由职业者人数达到2/3/4时,没有入住的租客可提供租金1/2/3.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>当电商哥人数达到2/3/4时，每次买入租客使其房租+1/2/3，每次卖出使其房租-3/-2/-1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>交租时:若体育哥人数比其他职业人数多2/3/4个,该职业租金+10/15/20</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>当地产哥人数达到2/3/4时,交租时使所有其他租客租金-1，每有一个租客受影响，该系列房租+1/2/3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>当艺术家人数达到2/3/4使:每有一名房客被消除，艺术哥房租+1/2/3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>当餐饮哥人数达到2/3/4时,每次完成交租,使所有非餐饮住客房租+1/2/3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>购买后触发:3天内无法买卖租客,然后全体房租提升等同于记者的房租</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>当旅游哥人数达到2/3/4时,每5次交租使其租金*2/3/4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>不提供房租,被消除时,获得所有邻居的售价返还</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>当医疗哥人数达到2/3/4时,若有租客天数超过10天，每一天使医疗哥租金+2/3/4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>每回合预算-1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>当教育哥人数达到2/3/4时,房租+1/2/3,售价+0/+1/+2</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -760,10 +770,10 @@
         <v>3</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>76</v>
+        <v>62</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.2">
@@ -785,10 +795,10 @@
         <v>7</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>78</v>
+        <v>64</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>79</v>
+        <v>65</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
@@ -805,10 +815,10 @@
         <v>8</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>75</v>
+        <v>61</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
@@ -819,16 +829,16 @@
         <v>10</v>
       </c>
       <c r="C7" t="s">
-        <v>73</v>
+        <v>60</v>
       </c>
       <c r="D7">
         <v>5001</v>
       </c>
       <c r="G7" t="s">
-        <v>108</v>
+        <v>89</v>
       </c>
       <c r="H7" t="s">
-        <v>109</v>
+        <v>90</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.2">
@@ -839,7 +849,7 @@
         <v>11</v>
       </c>
       <c r="C8" t="s">
-        <v>12</v>
+        <v>94</v>
       </c>
       <c r="D8">
         <v>5002</v>
@@ -848,10 +858,10 @@
         <v>1000</v>
       </c>
       <c r="G8" t="s">
-        <v>110</v>
+        <v>91</v>
       </c>
       <c r="H8" t="s">
-        <v>109</v>
+        <v>90</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.2">
@@ -859,19 +869,19 @@
         <v>3</v>
       </c>
       <c r="B9" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C9" t="s">
-        <v>96</v>
+        <v>80</v>
       </c>
       <c r="D9">
         <v>5003</v>
       </c>
       <c r="G9" t="s">
-        <v>108</v>
+        <v>89</v>
       </c>
       <c r="H9" t="s">
-        <v>109</v>
+        <v>90</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.2">
@@ -879,10 +889,10 @@
         <v>4</v>
       </c>
       <c r="B10" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C10" t="s">
-        <v>15</v>
+        <v>95</v>
       </c>
       <c r="D10">
         <v>5004</v>
@@ -891,13 +901,13 @@
         <v>500500</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>80</v>
+        <v>66</v>
       </c>
       <c r="G10" t="s">
-        <v>108</v>
+        <v>89</v>
       </c>
       <c r="H10" t="s">
-        <v>109</v>
+        <v>90</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.2">
@@ -905,10 +915,10 @@
         <v>5</v>
       </c>
       <c r="B11" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C11" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D11">
         <v>5005</v>
@@ -917,10 +927,10 @@
         <v>500</v>
       </c>
       <c r="G11" t="s">
-        <v>110</v>
+        <v>91</v>
       </c>
       <c r="H11" t="s">
-        <v>109</v>
+        <v>90</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.2">
@@ -928,19 +938,19 @@
         <v>6</v>
       </c>
       <c r="B12" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C12" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D12">
         <v>5006</v>
       </c>
       <c r="G12" t="s">
-        <v>108</v>
+        <v>89</v>
       </c>
       <c r="H12" t="s">
-        <v>109</v>
+        <v>90</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.2">
@@ -948,10 +958,10 @@
         <v>7</v>
       </c>
       <c r="B13" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C13" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D13">
         <v>5007</v>
@@ -960,10 +970,10 @@
         <v>1</v>
       </c>
       <c r="G13" t="s">
-        <v>110</v>
+        <v>91</v>
       </c>
       <c r="H13" t="s">
-        <v>109</v>
+        <v>90</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.2">
@@ -971,10 +981,10 @@
         <v>8</v>
       </c>
       <c r="B14" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C14" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D14">
         <v>5008</v>
@@ -983,7 +993,7 @@
         <v>1</v>
       </c>
       <c r="G14" t="s">
-        <v>111</v>
+        <v>92</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.2">
@@ -991,25 +1001,25 @@
         <v>20</v>
       </c>
       <c r="B15" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C15" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D15">
         <v>5020</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>82</v>
+        <v>68</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>82</v>
+        <v>68</v>
       </c>
       <c r="G15" t="s">
-        <v>110</v>
+        <v>91</v>
       </c>
       <c r="H15" t="s">
-        <v>109</v>
+        <v>90</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.2">
@@ -1017,25 +1027,25 @@
         <v>21</v>
       </c>
       <c r="B16" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C16" t="s">
-        <v>95</v>
+        <v>79</v>
       </c>
       <c r="D16">
         <v>5021</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>81</v>
+        <v>67</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>81</v>
+        <v>67</v>
       </c>
       <c r="G16" t="s">
-        <v>108</v>
+        <v>89</v>
       </c>
       <c r="H16" t="s">
-        <v>109</v>
+        <v>90</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.2">
@@ -1043,25 +1053,25 @@
         <v>22</v>
       </c>
       <c r="B17" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C17" t="s">
-        <v>107</v>
+        <v>88</v>
       </c>
       <c r="D17">
         <v>5022</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>82</v>
+        <v>68</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>83</v>
+        <v>69</v>
       </c>
       <c r="G17" t="s">
-        <v>108</v>
+        <v>89</v>
       </c>
       <c r="H17" t="s">
-        <v>109</v>
+        <v>90</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.2">
@@ -1069,22 +1079,22 @@
         <v>23</v>
       </c>
       <c r="B18" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C18" t="s">
-        <v>97</v>
+        <v>81</v>
       </c>
       <c r="D18">
         <v>5023</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>84</v>
+        <v>70</v>
       </c>
       <c r="G18" t="s">
-        <v>108</v>
+        <v>89</v>
       </c>
       <c r="H18" t="s">
-        <v>109</v>
+        <v>90</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.2">
@@ -1092,25 +1102,25 @@
         <v>24</v>
       </c>
       <c r="B19" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C19" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D19">
         <v>5024</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>81</v>
+        <v>67</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>81</v>
+        <v>67</v>
       </c>
       <c r="G19" t="s">
-        <v>110</v>
+        <v>91</v>
       </c>
       <c r="H19" t="s">
-        <v>109</v>
+        <v>90</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.2">
@@ -1118,19 +1128,19 @@
         <v>25</v>
       </c>
       <c r="B20" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C20" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D20">
         <v>5025</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>85</v>
+        <v>71</v>
       </c>
       <c r="G20" t="s">
-        <v>111</v>
+        <v>92</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.2">
@@ -1138,19 +1148,19 @@
         <v>26</v>
       </c>
       <c r="B21" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C21" t="s">
-        <v>106</v>
+        <v>87</v>
       </c>
       <c r="D21">
         <v>5026</v>
       </c>
       <c r="G21" t="s">
-        <v>108</v>
+        <v>89</v>
       </c>
       <c r="H21" t="s">
-        <v>109</v>
+        <v>90</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.2">
@@ -1158,25 +1168,25 @@
         <v>27</v>
       </c>
       <c r="B22" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C22" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D22">
         <v>5027</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>82</v>
+        <v>68</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>82</v>
+        <v>68</v>
       </c>
       <c r="G22" t="s">
-        <v>108</v>
+        <v>89</v>
       </c>
       <c r="H22" t="s">
-        <v>109</v>
+        <v>90</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.2">
@@ -1184,25 +1194,25 @@
         <v>28</v>
       </c>
       <c r="B23" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C23" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D23">
         <v>5028</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>86</v>
+        <v>72</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>82</v>
+        <v>68</v>
       </c>
       <c r="G23" t="s">
-        <v>108</v>
+        <v>89</v>
       </c>
       <c r="H23" t="s">
-        <v>109</v>
+        <v>90</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.2">
@@ -1210,22 +1220,22 @@
         <v>29</v>
       </c>
       <c r="B24" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C24" t="s">
-        <v>99</v>
+        <v>83</v>
       </c>
       <c r="D24">
         <v>5029</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>81</v>
+        <v>67</v>
       </c>
       <c r="G24" t="s">
-        <v>108</v>
+        <v>89</v>
       </c>
       <c r="H24" t="s">
-        <v>109</v>
+        <v>90</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.2">
@@ -1233,22 +1243,22 @@
         <v>30</v>
       </c>
       <c r="B25" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C25" t="s">
-        <v>98</v>
+        <v>82</v>
       </c>
       <c r="D25">
         <v>5030</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>81</v>
+        <v>67</v>
       </c>
       <c r="G25" t="s">
-        <v>108</v>
+        <v>89</v>
       </c>
       <c r="H25" t="s">
-        <v>109</v>
+        <v>90</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.2">
@@ -1256,22 +1266,22 @@
         <v>31</v>
       </c>
       <c r="B26" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C26" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D26">
         <v>5031</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>81</v>
+        <v>67</v>
       </c>
       <c r="G26" t="s">
-        <v>108</v>
+        <v>89</v>
       </c>
       <c r="H26" t="s">
-        <v>109</v>
+        <v>90</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.2">
@@ -1279,25 +1289,25 @@
         <v>32</v>
       </c>
       <c r="B27" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C27" t="s">
-        <v>100</v>
+        <v>84</v>
       </c>
       <c r="D27">
         <v>5032</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>81</v>
+        <v>67</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>87</v>
+        <v>73</v>
       </c>
       <c r="G27" t="s">
-        <v>108</v>
+        <v>89</v>
       </c>
       <c r="H27" t="s">
-        <v>109</v>
+        <v>90</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.2">
@@ -1305,25 +1315,25 @@
         <v>33</v>
       </c>
       <c r="B28" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C28" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D28">
         <v>5033</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>81</v>
+        <v>67</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="G28" t="s">
-        <v>108</v>
+        <v>89</v>
       </c>
       <c r="H28" t="s">
-        <v>109</v>
+        <v>90</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.2">
@@ -1331,25 +1341,25 @@
         <v>34</v>
       </c>
       <c r="B29" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C29" t="s">
-        <v>101</v>
+        <v>85</v>
       </c>
       <c r="D29">
         <v>5034</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>81</v>
+        <v>67</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>87</v>
+        <v>73</v>
       </c>
       <c r="G29" t="s">
-        <v>108</v>
+        <v>89</v>
       </c>
       <c r="H29" t="s">
-        <v>109</v>
+        <v>90</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.2">
@@ -1357,19 +1367,19 @@
         <v>35</v>
       </c>
       <c r="B30" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C30" t="s">
-        <v>102</v>
+        <v>86</v>
       </c>
       <c r="D30">
         <v>5035</v>
       </c>
       <c r="G30" t="s">
-        <v>108</v>
+        <v>89</v>
       </c>
       <c r="H30" t="s">
-        <v>109</v>
+        <v>90</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.2">
@@ -1377,25 +1387,25 @@
         <v>50</v>
       </c>
       <c r="B31" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C31" t="s">
-        <v>47</v>
+        <v>96</v>
       </c>
       <c r="D31">
         <v>5050</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>91</v>
+        <v>77</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>82</v>
+        <v>68</v>
       </c>
       <c r="G31" t="s">
-        <v>108</v>
+        <v>89</v>
       </c>
       <c r="H31" t="s">
-        <v>109</v>
+        <v>90</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.2">
@@ -1403,25 +1413,25 @@
         <v>51</v>
       </c>
       <c r="B32" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="C32" t="s">
-        <v>49</v>
+        <v>97</v>
       </c>
       <c r="D32">
         <v>5051</v>
       </c>
       <c r="E32" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="F32" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G32" t="s">
         <v>91</v>
       </c>
-      <c r="F32" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="G32" t="s">
-        <v>110</v>
-      </c>
       <c r="H32" t="s">
-        <v>109</v>
+        <v>90</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.2">
@@ -1429,25 +1439,25 @@
         <v>52</v>
       </c>
       <c r="B33" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="C33" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="D33">
         <v>5052</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>91</v>
+        <v>77</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>82</v>
+        <v>68</v>
       </c>
       <c r="G33" t="s">
-        <v>108</v>
+        <v>89</v>
       </c>
       <c r="H33" t="s">
-        <v>109</v>
+        <v>90</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.2">
@@ -1455,25 +1465,25 @@
         <v>53</v>
       </c>
       <c r="B34" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="C34" t="s">
-        <v>52</v>
+        <v>99</v>
       </c>
       <c r="D34">
         <v>5053</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>91</v>
+        <v>77</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>82</v>
+        <v>68</v>
       </c>
       <c r="G34" t="s">
-        <v>108</v>
+        <v>89</v>
       </c>
       <c r="H34" t="s">
-        <v>109</v>
+        <v>90</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.2">
@@ -1481,22 +1491,22 @@
         <v>54</v>
       </c>
       <c r="B35" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="C35" t="s">
-        <v>54</v>
+        <v>110</v>
       </c>
       <c r="D35">
         <v>5054</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>91</v>
+        <v>77</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>89</v>
+        <v>75</v>
       </c>
       <c r="G35" t="s">
-        <v>111</v>
+        <v>92</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.2">
@@ -1504,25 +1514,25 @@
         <v>55</v>
       </c>
       <c r="B36" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="C36" t="s">
-        <v>56</v>
+        <v>100</v>
       </c>
       <c r="D36">
         <v>5055</v>
       </c>
       <c r="E36" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="F36" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G36" t="s">
         <v>91</v>
       </c>
-      <c r="F36" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="G36" t="s">
-        <v>110</v>
-      </c>
       <c r="H36" t="s">
-        <v>109</v>
+        <v>90</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.2">
@@ -1530,25 +1540,25 @@
         <v>56</v>
       </c>
       <c r="B37" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="C37" t="s">
-        <v>58</v>
+        <v>101</v>
       </c>
       <c r="D37">
         <v>5056</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>91</v>
+        <v>77</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>90</v>
+        <v>76</v>
       </c>
       <c r="G37" t="s">
-        <v>108</v>
+        <v>89</v>
       </c>
       <c r="H37" t="s">
-        <v>109</v>
+        <v>90</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.2">
@@ -1556,25 +1566,25 @@
         <v>57</v>
       </c>
       <c r="B38" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="C38" t="s">
-        <v>74</v>
+        <v>102</v>
       </c>
       <c r="D38">
         <v>5057</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>91</v>
+        <v>77</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>82</v>
+        <v>68</v>
       </c>
       <c r="G38" t="s">
-        <v>108</v>
+        <v>89</v>
       </c>
       <c r="H38" t="s">
-        <v>109</v>
+        <v>90</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.2">
@@ -1582,25 +1592,25 @@
         <v>58</v>
       </c>
       <c r="B39" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="C39" t="s">
-        <v>61</v>
+        <v>103</v>
       </c>
       <c r="D39">
         <v>5058</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>91</v>
+        <v>77</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>82</v>
+        <v>68</v>
       </c>
       <c r="G39" t="s">
-        <v>108</v>
+        <v>89</v>
       </c>
       <c r="H39" t="s">
-        <v>109</v>
+        <v>90</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.2">
@@ -1608,7 +1618,7 @@
         <v>59</v>
       </c>
       <c r="B40" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="C40" t="s">
         <v>104</v>
@@ -1617,16 +1627,16 @@
         <v>5059</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>91</v>
+        <v>77</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>82</v>
+        <v>68</v>
       </c>
       <c r="G40" t="s">
-        <v>108</v>
+        <v>89</v>
       </c>
       <c r="H40" t="s">
-        <v>109</v>
+        <v>90</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.2">
@@ -1634,22 +1644,22 @@
         <v>60</v>
       </c>
       <c r="B41" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="C41" t="s">
-        <v>64</v>
+        <v>105</v>
       </c>
       <c r="D41">
         <v>5060</v>
       </c>
-      <c r="F41" s="2" t="s">
-        <v>92</v>
+      <c r="F41">
+        <v>3</v>
       </c>
       <c r="G41" t="s">
-        <v>110</v>
+        <v>91</v>
       </c>
       <c r="H41" t="s">
-        <v>109</v>
+        <v>90</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.2">
@@ -1657,25 +1667,25 @@
         <v>61</v>
       </c>
       <c r="B42" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="C42" t="s">
-        <v>66</v>
+        <v>106</v>
       </c>
       <c r="D42">
         <v>5061</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>91</v>
+        <v>77</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>82</v>
+        <v>68</v>
       </c>
       <c r="G42" t="s">
-        <v>108</v>
+        <v>89</v>
       </c>
       <c r="H42" t="s">
-        <v>109</v>
+        <v>90</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.2">
@@ -1683,25 +1693,25 @@
         <v>62</v>
       </c>
       <c r="B43" t="s">
-        <v>67</v>
+        <v>56</v>
       </c>
       <c r="C43" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="D43">
         <v>5062</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>82</v>
+        <v>68</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>91</v>
+        <v>77</v>
       </c>
       <c r="G43" t="s">
-        <v>108</v>
+        <v>89</v>
       </c>
       <c r="H43" t="s">
-        <v>109</v>
+        <v>90</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.2">
@@ -1709,25 +1719,25 @@
         <v>63</v>
       </c>
       <c r="B44" t="s">
-        <v>68</v>
+        <v>57</v>
       </c>
       <c r="C44" t="s">
-        <v>69</v>
+        <v>108</v>
       </c>
       <c r="D44">
         <v>5063</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>91</v>
+        <v>77</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>91</v>
+        <v>77</v>
       </c>
       <c r="G44" t="s">
-        <v>108</v>
+        <v>89</v>
       </c>
       <c r="H44" t="s">
-        <v>109</v>
+        <v>90</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.2">
@@ -1735,31 +1745,31 @@
         <v>64</v>
       </c>
       <c r="B45" t="s">
-        <v>70</v>
+        <v>58</v>
       </c>
       <c r="C45" t="s">
-        <v>71</v>
+        <v>109</v>
       </c>
       <c r="D45">
         <v>5064</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>93</v>
+        <v>78</v>
       </c>
       <c r="G45" t="s">
-        <v>111</v>
+        <v>92</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
-        <v>72</v>
+        <v>59</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="E7:F30 F35 F32 F31 E41:F41 E45:F45 F34 F37 F44 F39 F40" numberStoredAsText="1"/>
+    <ignoredError sqref="E7:F30 F35 F32 F31 E41 E45:F45 F34 F37 F44 F39 F40" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>